--- a/stories/arbres/ATOM-SOC.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte. Papa dit : c'est un métier. Gwenaëlle dit : chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants. Papa dit : c'est un métier. Gwenaëlle dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Maman dit : c'est un métier. Gwenaëlle dit : médecin. Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire. Papa dit : c'est un métier. Gwenaëlle dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+          <t>Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte. C'est un métier. Chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,23 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte.
+papa|C'est un métier.
+enfant-f|Chauffeur.
+narrateur|Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants.
+papa|C'est un métier.
+enfant-f|Boulanger.
+narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur.
+maman|C'est un métier.
+enfant-f|Médecin.
+narrateur|Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire.
+papa|C'est un métier.
+enfant-f|Maîtresse.
+narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chauffeur ouvre la porte. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gwenaëlle serre la main de papa. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1322,6 +1327,7 @@
 narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Le chauffeur ouvre la porte. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Gwenaëlle a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Gwenaëlle serre la main de papa. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gwenaëlle nomme les métiers</t>
+          <t>Les filets du port</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut voir les filets au port. Une gerbe d'eau saute. Ils reculent derrière la rambarde. Puis le boulanger du port glisse un pain chaud dans le papier.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte. C'est un métier. Chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+          <t>Les filets sentent le sel et l'eau. Ils pendent le long du quai, encore goutte à goutte. Une mouette crie au-dessus du mât. Raphaël vit près d'ici, avec papa et maman. Le bois du quai est gris, piqué de sel. Je veux voir les filets, papa. On reste sur le quai. Près de moi. En ce moment, Raphaël pose les deux mains sur la rambarde. Le métal est froid, un peu collant. Un marin tire un filet, lentement. L'eau tombe en perles, sur le bois. Il est fort. C'est le marin. C'est son métier. Il ramène les filets. Oui. Le filet glisse, trop vite, un instant. Une gerbe d'eau saute vers les chaussures. Oh. On recule d'un pas. On reste derrière la rambarde ? Oui. Raphaël essuie une goutte sur sa manche. Ça sent encore plus le sel. Mes mains sont mouillées. Le marin travaille dans l'eau. Toi, tu regardes. Le marin range le filet en rond, tout serré. Une écaille brille, puis elle disparaît. Merci, marin ! Merci. Bravo, Raphaël. Tu as regardé sans te pencher trop. J'ai faim, maintenant. Le boulanger du port est ouvert. Du pain, avec le sel encore dans l'air.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte. Papa dit : c'est un &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;. Gwenaëlle dit : chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants. Papa dit : c'est un métier. Gwenaëlle dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Maman dit : c'est un métier. Gwenaëlle dit : médecin. Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire. Papa dit : c'est un métier. Gwenaëlle dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les filets sentent le sel et l'eau. Ils pendent le long du quai, encore goutte à goutte. Une mouette crie au-dessus du mât. Raphaël vit près d'ici, avec papa et maman. Le bois du quai est gris, piqué de sel. Je veux voir les filets, papa. On reste sur le quai. Près de moi. En ce moment, Raphaël pose les deux mains sur la rambarde. Le métal est froid, un peu collant. Un marin tire un filet, lentement. L'eau tombe en perles, sur le bois. Il est fort. C'est le marin. C'est son métier. Il ramène les filets. Oui. Le filet glisse, trop vite, un instant. Une gerbe d'eau saute vers les chaussures. Oh. On recule d'un pas. On reste derrière la rambarde ? Oui. Raphaël essuie une goutte sur sa manche. Ça sent encore plus le sel. Mes mains sont mouillées. Le marin travaille dans l'eau. Toi, tu regardes. Le marin range le filet en rond, tout serré. Une écaille brille, puis elle disparaît. Merci, marin ! Merci. Bravo, Raphaël. Tu as regardé sans te pencher trop. J'ai faim, maintenant. Le boulanger du port est ouvert. Du pain, avec le sel encore dans l'air.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,22 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle marche avec papa. Maman les rejoint à l'arrêt. Ils prennent le bus. Le chauffeur ouvre la porte.
-papa|C'est un métier.
-enfant-f|Chauffeur.
-narrateur|Le chauffeur fait un geste utile. Il conduit. Ensuite, la boulangerie. Ça sent le pain chaud. Le boulanger pose les croissants.
-papa|C'est un métier.
-enfant-f|Boulanger.
-narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur.
-maman|C'est un métier.
-enfant-f|Médecin.
-narrateur|Le médecin fait un geste utile. Il soigne. Après, ils arrivent à l'école. La maîtresse lit une histoire.
-papa|C'est un métier.
-enfant-f|Maîtresse.
-narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les filets sentent le sel et l'eau.
+narrateur|Ils pendent le long du quai, encore goutte à goutte.
+narrateur|Une mouette crie au-dessus du mât.
+narrateur|Raphaël vit près d'ici, avec papa et maman.
+narrateur|Le bois du quai est gris, piqué de sel.
+enfant-m|Je veux voir les filets, papa.
+papa|On reste sur le quai.
+maman|Près de moi.
+narrateur|En ce moment, Raphaël pose les deux mains sur la rambarde.
+narrateur|Le métal est froid, un peu collant.
+narrateur|Un marin tire un filet, lentement.
+narrateur|L'eau tombe en perles, sur le bois.
+enfant-m|Il est fort.
+papa|C'est le marin.
+papa|C'est son métier.
+enfant-m|Il ramène les filets.
+maman|Oui.
+narrateur|Le filet glisse, trop vite, un instant.
+narrateur|Une gerbe d'eau saute vers les chaussures.
+maman|Oh.
+maman|On recule d'un pas.
+papa|On reste derrière la rambarde ?
+enfant-m|Oui.
+narrateur|Raphaël essuie une goutte sur sa manche.
+narrateur|Ça sent encore plus le sel.
+enfant-m|Mes mains sont mouillées.
+maman|Le marin travaille dans l'eau.
+papa|Toi, tu regardes.
+narrateur|Le marin range le filet en rond, tout serré.
+narrateur|Une écaille brille, puis elle disparaît.
+enfant-m|Merci, marin !
+papa|Merci.
+maman|Bravo, Raphaël.
+maman|Tu as regardé sans te pencher trop.
+enfant-m|J'ai faim, maintenant.
+papa|Le boulanger du port est ouvert.
+maman|Du pain, avec le sel encore dans l'air.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1352,27 +1387,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Le marin tire les filets. C'est quoi ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Le marin tire les filets. C'est quoi ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Le chauffeur ouvre la porte. C'est quoi ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chauffeur ouvre la porte. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Le chauffeur ouvre la porte. C'est quoi ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>un métier</t>
+          <t>métier</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>un métier | métier | chauffeur | le chauffeur</t>
+          <t>métier | un métier | son métier | le métier | c'est un métier</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il fait un geste utile. C'est quoi ?</t>
+          <t>Il ramène les filets. C'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,14 +1464,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chauffeur ouvre la porte. C'est quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le marin tire les filets.
+narrateur|C'est quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+          <t>Ils quittent le quai, pas à pas. Le bois sonne sous les chaussures. La boutique du pain est toute proche, peinte en bleu. Ça sent le beurre, après le sel. Le boulanger ! Oui. Lui aussi a un métier. Il prépare le pain. Pour nous. Raphaël a encore une goutte de sel au poignet. Il la sent, puis il tend les mains au sac. Un pain long, encore chaud, plie le papier. Merci. Tu le portes ? Oui. Les filets, et le pain. Deux métiers. Oui. Une mouette les suit un instant, puis elle part.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle a nommé les &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;s. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils quittent le quai, pas à pas. Le bois sonne sous les chaussures. La boutique du pain est toute proche, peinte en bleu. Ça sent le beurre, après le sel. Le boulanger ! Oui. Lui aussi a un métier. Il prépare le pain. Pour nous. Raphaël a encore une goutte de sel au poignet. Il la sent, puis il tend les mains au sac. Un pain long, encore chaud, plie le papier. Merci. Tu le portes ? Oui. Les filets, et le pain. Deux métiers. Oui. Une mouette les suit un instant, puis elle part.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1604,7 +1639,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1715,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Ils quittent le quai, pas à pas.
+narrateur|Le bois sonne sous les chaussures.
+narrateur|La boutique du pain est toute proche, peinte en bleu.
+narrateur|Ça sent le beurre, après le sel.
+enfant-m|Le boulanger !
+maman|Oui.
+maman|Lui aussi a un métier.
+papa|Il prépare le pain.
+enfant-m|Pour nous.
+narrateur|Raphaël a encore une goutte de sel au poignet.
+narrateur|Il la sent, puis il tend les mains au sac.
+narrateur|Un pain long, encore chaud, plie le papier.
+papa|Merci.
+maman|Tu le portes ?
+enfant-m|Oui.
+papa|Les filets, et le pain.
+enfant-m|Deux métiers.
+maman|Oui.
+narrateur|Une mouette les suit un instant, puis elle part.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1760,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gwenaëlle serre la main de papa. Ils rentrent à la maison.</t>
+          <t>Sur un banc face à l'eau, ils s'assoient. Le pain craque, tout fort. Des miettes tombent, trop petites pour les poissons. Ça sent le sel, et le four. Oui. Le marin, puis le boulanger. Tu as vu les filets ? Oui. Ils gouttaient. Et toi, tu es resté derrière la rambarde. Merci d'avoir reculé, tout de suite. L'eau clapote contre le bois, tout régulier. Le sac de pain pèse encore un peu, sur les genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gwenaëlle serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur un banc face à l'eau, ils s'assoient. Le pain craque, tout fort. Des miettes tombent, trop petites pour les poissons. Ça sent le sel, et le four. Oui. Le marin, puis le boulanger. Tu as vu les filets ? Oui. Ils gouttaient. Et toi, tu es resté derrière la rambarde. Merci d'avoir reculé, tout de suite. L'eau clapote contre le bois, tout régulier. Le sac de pain pèse encore un peu, sur les genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1776,7 +1828,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1900,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gwenaëlle serre la main de papa. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sur un banc face à l'eau, ils s'assoient.
+narrateur|Le pain craque, tout fort.
+narrateur|Des miettes tombent, trop petites pour les poissons.
+enfant-m|Ça sent le sel, et le four.
+papa|Oui.
+papa|Le marin, puis le boulanger.
+maman|Tu as vu les filets ?
+enfant-m|Oui.
+enfant-m|Ils gouttaient.
+maman|Et toi, tu es resté derrière la rambarde.
+papa|Merci d'avoir reculé, tout de suite.
+narrateur|L'eau clapote contre le bois, tout régulier.
+narrateur|Le sac de pain pèse encore un peu, sur les genoux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1939,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une dernière goutte tombe d'un filet, au loin. Elle fait un rond, puis plus rien. Le pain est bon. Oui. Le port garde le sel. Raphaël essuie sa manche, déjà sèche. Le papier du pain claque un peu, dans le vent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une dernière goutte tombe d'un filet, au loin. Elle fait un rond, puis plus rien. Le pain est bon. Oui. Le port garde le sel. Raphaël essuie sa manche, déjà sèche. Le papier du pain claque un peu, dans le vent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1944,7 +2007,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2079,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Une dernière goutte tombe d'un filet, au loin.
+narrateur|Elle fait un rond, puis plus rien.
+enfant-m|Le pain est bon.
+maman|Oui.
+papa|Le port garde le sel.
+narrateur|Raphaël essuie sa manche, déjà sèche.
+narrateur|Le papier du pain claque un peu, dans le vent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bus, boulangerie, cabinet, école</t>
+          <t>quai, filets, rambarde, boutique bleue du pain, banc face à l'eau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gwenaëlle, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
